--- a/public/price-list.xlsx
+++ b/public/price-list.xlsx
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -119,8 +119,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -202,6 +206,661 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -493,15 +1152,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -526,25 +1186,30 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Фото</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Описание</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Цена, руб.</t>
         </is>
@@ -557,629 +1222,653 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="78" customHeight="1">
       <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>OstovPark C1-8</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Классическая форма для аллей и пешеходных дорожек. Равномерное рассеивание света, защита IP65.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n"/>
-    </row>
-    <row r="7">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="78" customHeight="1">
       <c r="A7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>OstovPark K1-8</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Современный дизайн для парков и скверов. Оптика европейского качества, долгий срок службы.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n"/>
-    </row>
-    <row r="8">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="78" customHeight="1">
       <c r="A8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>OstovPark X1-8</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>X-образная конструкция на 2 блока. Подходит для освещения широких зон и перекрёстков дорожек.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n"/>
-    </row>
-    <row r="9">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="78" customHeight="1">
       <c r="A9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>OstovPark L1-8</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>L-образная форма для монтажа на опору у стен и ограждений. Направленный световой поток.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n"/>
-    </row>
-    <row r="10">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="78" customHeight="1">
       <c r="A10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>OstovPark Y1-8</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Y-образная конструкция на 4 блока. Максимальное покрытие для больших парковых территорий.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n"/>
-    </row>
-    <row r="11">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="78" customHeight="1">
       <c r="A11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>OstovPark T1-8</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Т-образная конструкция с двумя световыми блоками. Освещение аллей и широких пешеходных зон.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n"/>
-    </row>
-    <row r="12">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="78" customHeight="1">
       <c r="A12" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>OstovPark Triple1-8</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Тройная конструкция с тремя световыми блоками. Для освещения перекрёстков и площадей.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n"/>
-    </row>
-    <row r="13">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="78" customHeight="1">
       <c r="A13" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>OstovPark Q1-8</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Четырёхсторонняя конструкция для равномерного освещения больших открытых пространств.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n"/>
-    </row>
-    <row r="14">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="78" customHeight="1">
       <c r="A14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>OstovPark CL1-8</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Компактная модель с одним направленным блоком. Для входных групп и узких дорожек.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n"/>
-    </row>
-    <row r="15">
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="78" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>OstovPark CT1-8</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Комбинированная конструкция с верхним и боковым блоком. Универсальное решение для парков.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-    </row>
-    <row r="16">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="78" customHeight="1">
       <c r="A16" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>OstovPark CY1-8</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Y-образная конструкция с двумя световыми блоками. Стильное решение для аллей и парковых зон.</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-    </row>
-    <row r="17">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="78" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>OstovPark CX1-8</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Изогнутая конструкция с одним световым блоком. Элегантный дизайн для парков и пешеходных зон.</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n"/>
-    </row>
-    <row r="18">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="78" customHeight="1">
       <c r="A18" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Остов Парк Арт 1-8</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Элегантный парковый светильник с круглым плафоном и изящными дугообразными кронштейнами. Тёплый свет для парков, скверов и набережных.</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n"/>
-    </row>
-    <row r="19">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="78" customHeight="1">
       <c r="A19" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Остов парк модерн 4</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Опора с четырьмя направленными световыми модулями в современном дизайне. Подходит для парков, скверов и пешеходных зон.</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-    </row>
-    <row r="20">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="78" customHeight="1">
       <c r="A20" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Остов Парк Маяк 5</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Декоративный bollard-светильник с ажурным узором из органических форм. Создаёт уютную атмосферу вдоль пешеходных дорожек и в парковых зонах.</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
-    </row>
-    <row r="21">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="78" customHeight="1">
       <c r="A21" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>OstovPark Z-1</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Круглый плафон на изогнутых кронштейнах-каплях. Лаконичный дизайн для парков, скверов и придомовых территорий.</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="78" customHeight="1">
       <c r="A22" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>OstovPark Z-2</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Плафон в форме летающей тарелки на кронштейне-дереве. Оригинальный дизайн для парков, скверов и общественных пространств.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n"/>
-    </row>
-    <row r="23">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="78" customHeight="1">
       <c r="A23" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>OstovPark Z-3</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Кольцевой светодиодный плафон на компактном кронштейне. Современный акцентный дизайн для парков и общественных пространств.</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n"/>
-    </row>
-    <row r="24">
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="78" customHeight="1">
       <c r="A24" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>OstovPark Z-4</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Консольный светильник на изогнутом кронштейне с плоским плафоном. Направленный световой поток для дорожек и аллей.</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n"/>
-    </row>
-    <row r="25">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="78" customHeight="1">
       <c r="A25" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>OstovPark Z-2-1</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Круглый плафон на изящном V-образном кронштейне. Классический силуэт для парков, скверов и придомовых территорий.</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n"/>
-    </row>
-    <row r="26">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="78" customHeight="1">
       <c r="A26" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>OstovPark L-12</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Овальный плафон с направленной LED-матрицей на изогнутом кронштейне. Аэродинамичный дизайн для аллей и парковых дорожек.</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n"/>
-    </row>
-    <row r="27">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="78" customHeight="1">
       <c r="A27" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>OstovPark V-21</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>Дугообразный консольный светильник с вытянутой LED-панелью. Плавные линии и направленный свет для дорожек и уличного освещения.</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="n"/>
-    </row>
-    <row r="28">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="78" customHeight="1">
       <c r="A28" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>OstovPark Z-5</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Светильник-гриб с широкой круглой шляпкой и прозрачным цилиндрическим плафоном. Классический дизайн для парков и придомовых территорий.</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="n"/>
-    </row>
-    <row r="29">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="78" customHeight="1">
       <c r="A29" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>OstovPark — парковые светильники IP65</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>OstovPark — парковые светильники IP65</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>OstovPark L-11</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>Уличный светильник с четырёхсекционной LED-матрицей на консольном креплении. Мощный направленный свет для дорог и парковых магистралей.</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -1188,60 +1877,62 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="78" customHeight="1">
       <c r="A31" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Ostov Terra — грунтовые и встраиваемые светильники IP67</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Остов Терра Спарк</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Светильник ландшафтный Остов Терра Спарк</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>Ландшафтный светильник на штыре для установки в грунт. Направленный световой поток, поворотная головка. Подходит для подсветки клумб, дорожек и архитектурных элементов.</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="n"/>
-    </row>
-    <row r="32">
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="78" customHeight="1">
       <c r="A32" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Ostov Terra — грунтовые и встраиваемые светильники IP67</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Остов Терра Брусчатка</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Светильник ландшафтный Остов Терра Брусчатка</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Встраиваемый светильник-брусчатка для мощения дорожек и площадок. Укладывается вровень с покрытием, степень защиты IP67. Создаёт эффектную подсветку пешеходных зон.</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Цены указываются по запросу в зависимости от объёма и комплектации. Свяжитесь с отделом продаж для расчёта.</t>
         </is>
@@ -1249,12 +1940,13 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>